--- a/gamedata/Guest.xlsx
+++ b/gamedata/Guest.xlsx
@@ -690,39 +690,39 @@
     </row>
     <row r="5" ht="15.75" customHeight="1" s="4">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>501</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>趕時間的上班族</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="J5" t="b">
+      <c r="J5" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="b">
+      <c r="K5" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="0" t="inlineStr">
         <is>
           <t>1^301</t>
         </is>
@@ -730,39 +730,39 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" s="4">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" t="n">
+      <c r="B6" s="0" t="n">
         <v>502</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>嚴格的美食家</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="J6" t="b">
+      <c r="J6" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="b">
+      <c r="K6" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="0" t="inlineStr">
         <is>
           <t>2^301,1^301</t>
         </is>
@@ -770,39 +770,39 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" s="4">
       <c r="A7" s="3" t="n"/>
-      <c r="B7" t="n">
+      <c r="B7" s="0" t="n">
         <v>503</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>悠哉的常客</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="b">
+      <c r="J7" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K7" t="b">
+      <c r="K7" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="0" t="inlineStr">
         <is>
           <t>3^301</t>
         </is>
@@ -810,27 +810,328 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" s="4">
       <c r="A8" s="3" t="n"/>
+      <c r="B8" t="n">
+        <v>511</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>排隊熟客</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3^352</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2^301</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="4">
       <c r="A9" s="3" t="n"/>
+      <c r="B9" t="n">
+        <v>512</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>聞香而來</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2^352</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="4">
       <c r="A10" s="3" t="n"/>
+      <c r="B10" t="n">
+        <v>513</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>大胃王</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4^311,8^352</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="4">
       <c r="A11" s="3" t="n"/>
+      <c r="B11" t="n">
+        <v>514</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>路過食客</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3^301</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="4">
       <c r="A12" s="3" t="n"/>
+      <c r="B12" t="n">
+        <v>515</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>美食部落客</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3^352</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2^301</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="4">
       <c r="A13" s="3" t="n"/>
+      <c r="B13" t="n">
+        <v>516</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>沉默旅人</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="4">
       <c r="A14" s="3" t="n"/>
+      <c r="B14" t="n">
+        <v>517</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>急性子情侶</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2^352</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="4">
       <c r="A15" s="3" t="n"/>
+      <c r="B15" t="n">
+        <v>518</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>夜班司機</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4^301,2^301</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="4">
       <c r="A16" s="3" t="n"/>
